--- a/ipar40tk-server/simulator/baselines/high-rpm_idle_filled_simulator.xlsx
+++ b/ipar40tk-server/simulator/baselines/high-rpm_idle_filled_simulator.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bprof2025\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMPACT-MAPS\COMPACT-MAPS\ipar40tk-server\simulator\baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425E47C2-438E-4815-A9A4-1BD44B7F5FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C4B57A52-DFAF-48A6-9B0D-785860DCE190}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -7010,8 +7009,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7376,11 +7375,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0857CCDF-1612-4277-8DD4-0E10852E14AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F817"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7400,7 +7399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -7420,7 +7419,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -7440,7 +7439,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -7460,7 +7459,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -7480,7 +7479,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -7500,7 +7499,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -7520,7 +7519,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7540,7 +7539,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -7560,7 +7559,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7580,7 +7579,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -7600,7 +7599,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -7620,7 +7619,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -7640,7 +7639,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -7660,7 +7659,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -7700,7 +7699,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -7720,7 +7719,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -7740,7 +7739,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -7760,7 +7759,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -7780,7 +7779,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -7800,7 +7799,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -7820,7 +7819,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -7840,7 +7839,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -7860,7 +7859,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -7880,7 +7879,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -7900,7 +7899,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -7920,7 +7919,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -7940,7 +7939,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -7960,7 +7959,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -7980,7 +7979,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -8000,7 +7999,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -8020,7 +8019,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -8040,7 +8039,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -8060,7 +8059,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -8080,7 +8079,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -8100,7 +8099,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -8120,7 +8119,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -8140,7 +8139,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -8160,7 +8159,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -8180,7 +8179,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -8200,7 +8199,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -8220,7 +8219,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -8240,7 +8239,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -8260,7 +8259,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -8280,7 +8279,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -8300,7 +8299,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -8320,7 +8319,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -8340,7 +8339,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -8360,7 +8359,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -8380,7 +8379,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>55</v>
       </c>
@@ -8400,7 +8399,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>56</v>
       </c>
@@ -8420,7 +8419,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>57</v>
       </c>
@@ -8440,7 +8439,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>58</v>
       </c>
@@ -8460,7 +8459,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -8480,7 +8479,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>60</v>
       </c>
@@ -8500,7 +8499,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>61</v>
       </c>
@@ -8520,7 +8519,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>62</v>
       </c>
@@ -8540,7 +8539,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -8560,7 +8559,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>64</v>
       </c>
@@ -8580,7 +8579,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>65</v>
       </c>
@@ -8600,7 +8599,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -8620,7 +8619,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>67</v>
       </c>
@@ -8640,7 +8639,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>68</v>
       </c>
@@ -8660,7 +8659,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -8680,7 +8679,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>70</v>
       </c>
@@ -8700,7 +8699,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>71</v>
       </c>
@@ -8720,7 +8719,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>72</v>
       </c>
@@ -8740,7 +8739,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>73</v>
       </c>
@@ -8760,7 +8759,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>74</v>
       </c>
@@ -8780,7 +8779,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>75</v>
       </c>
@@ -8800,7 +8799,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -8820,7 +8819,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>77</v>
       </c>
@@ -8840,7 +8839,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>78</v>
       </c>
@@ -8860,7 +8859,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>79</v>
       </c>
@@ -8880,7 +8879,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>80</v>
       </c>
@@ -8900,7 +8899,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>81</v>
       </c>
@@ -8920,7 +8919,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>82</v>
       </c>
@@ -8940,7 +8939,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>83</v>
       </c>
@@ -8960,7 +8959,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -8980,7 +8979,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>85</v>
       </c>
@@ -9000,7 +8999,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>86</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>87</v>
       </c>
@@ -9040,7 +9039,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>88</v>
       </c>
@@ -9060,7 +9059,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>89</v>
       </c>
@@ -9080,7 +9079,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -9100,7 +9099,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>91</v>
       </c>
@@ -9120,7 +9119,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -9140,7 +9139,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>93</v>
       </c>
@@ -9160,7 +9159,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>94</v>
       </c>
@@ -9180,7 +9179,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>95</v>
       </c>
@@ -9200,7 +9199,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>96</v>
       </c>
@@ -9220,7 +9219,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>97</v>
       </c>
@@ -9240,7 +9239,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>98</v>
       </c>
@@ -9260,7 +9259,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>99</v>
       </c>
@@ -9280,7 +9279,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>100</v>
       </c>
@@ -9300,7 +9299,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>101</v>
       </c>
@@ -9320,7 +9319,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>102</v>
       </c>
@@ -9340,7 +9339,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>103</v>
       </c>
@@ -9360,7 +9359,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>104</v>
       </c>
@@ -9380,7 +9379,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>105</v>
       </c>
@@ -9400,7 +9399,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>106</v>
       </c>
@@ -9420,7 +9419,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -9440,7 +9439,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>108</v>
       </c>
@@ -9460,7 +9459,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>109</v>
       </c>
@@ -9480,7 +9479,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>110</v>
       </c>
@@ -9500,7 +9499,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>111</v>
       </c>
@@ -9520,7 +9519,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>112</v>
       </c>
@@ -9540,7 +9539,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>113</v>
       </c>
@@ -9560,7 +9559,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>114</v>
       </c>
@@ -9580,7 +9579,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -9600,7 +9599,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>116</v>
       </c>
@@ -9620,7 +9619,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>117</v>
       </c>
@@ -9640,7 +9639,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>118</v>
       </c>
@@ -9660,7 +9659,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>119</v>
       </c>
@@ -9680,7 +9679,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>120</v>
       </c>
@@ -9700,7 +9699,7 @@
         <v>1745</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>121</v>
       </c>
@@ -9720,7 +9719,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>122</v>
       </c>
@@ -9740,7 +9739,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>123</v>
       </c>
@@ -9760,7 +9759,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -9780,7 +9779,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>125</v>
       </c>
@@ -9800,7 +9799,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>126</v>
       </c>
@@ -9820,7 +9819,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>127</v>
       </c>
@@ -9840,7 +9839,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>128</v>
       </c>
@@ -9860,7 +9859,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>129</v>
       </c>
@@ -9880,7 +9879,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>130</v>
       </c>
@@ -9900,7 +9899,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>131</v>
       </c>
@@ -9920,7 +9919,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>132</v>
       </c>
@@ -9940,7 +9939,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>133</v>
       </c>
@@ -9960,7 +9959,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>134</v>
       </c>
@@ -9980,7 +9979,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>135</v>
       </c>
@@ -10000,7 +9999,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>136</v>
       </c>
@@ -10020,7 +10019,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -10040,7 +10039,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>138</v>
       </c>
@@ -10060,7 +10059,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>139</v>
       </c>
@@ -10080,7 +10079,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -10100,7 +10099,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>141</v>
       </c>
@@ -10120,7 +10119,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>142</v>
       </c>
@@ -10140,7 +10139,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>143</v>
       </c>
@@ -10160,7 +10159,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>144</v>
       </c>
@@ -10180,7 +10179,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -10200,7 +10199,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>146</v>
       </c>
@@ -10220,7 +10219,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>147</v>
       </c>
@@ -10240,7 +10239,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>148</v>
       </c>
@@ -10260,7 +10259,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>149</v>
       </c>
@@ -10280,7 +10279,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -10300,7 +10299,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>151</v>
       </c>
@@ -10320,7 +10319,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>152</v>
       </c>
@@ -10340,7 +10339,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -10360,7 +10359,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>154</v>
       </c>
@@ -10380,7 +10379,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>155</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>156</v>
       </c>
@@ -10420,7 +10419,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>157</v>
       </c>
@@ -10440,7 +10439,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -10460,7 +10459,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>159</v>
       </c>
@@ -10480,7 +10479,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>160</v>
       </c>
@@ -10500,7 +10499,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>161</v>
       </c>
@@ -10520,7 +10519,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>162</v>
       </c>
@@ -10540,7 +10539,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>163</v>
       </c>
@@ -10560,7 +10559,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>164</v>
       </c>
@@ -10580,7 +10579,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>165</v>
       </c>
@@ -10600,7 +10599,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>166</v>
       </c>
@@ -10620,7 +10619,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>167</v>
       </c>
@@ -10640,7 +10639,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>168</v>
       </c>
@@ -10660,7 +10659,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>169</v>
       </c>
@@ -10680,7 +10679,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -10700,7 +10699,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>171</v>
       </c>
@@ -10720,7 +10719,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>172</v>
       </c>
@@ -10740,7 +10739,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>173</v>
       </c>
@@ -10760,7 +10759,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>174</v>
       </c>
@@ -10780,7 +10779,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>175</v>
       </c>
@@ -10800,7 +10799,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>176</v>
       </c>
@@ -10820,7 +10819,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>177</v>
       </c>
@@ -10840,7 +10839,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>178</v>
       </c>
@@ -10860,7 +10859,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>179</v>
       </c>
@@ -10880,7 +10879,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>180</v>
       </c>
@@ -10900,7 +10899,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>181</v>
       </c>
@@ -10920,7 +10919,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>182</v>
       </c>
@@ -10940,7 +10939,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>183</v>
       </c>
@@ -10960,7 +10959,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>184</v>
       </c>
@@ -10980,7 +10979,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>185</v>
       </c>
@@ -11000,7 +10999,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>186</v>
       </c>
@@ -11020,7 +11019,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>187</v>
       </c>
@@ -11040,7 +11039,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>188</v>
       </c>
@@ -11060,7 +11059,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>189</v>
       </c>
@@ -11080,7 +11079,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>190</v>
       </c>
@@ -11100,7 +11099,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>191</v>
       </c>
@@ -11120,7 +11119,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>192</v>
       </c>
@@ -11140,7 +11139,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>193</v>
       </c>
@@ -11160,7 +11159,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>194</v>
       </c>
@@ -11180,7 +11179,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>195</v>
       </c>
@@ -11200,7 +11199,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>196</v>
       </c>
@@ -11220,7 +11219,7 @@
         <v>1815</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>197</v>
       </c>
@@ -11240,7 +11239,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -11260,7 +11259,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>199</v>
       </c>
@@ -11280,7 +11279,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>200</v>
       </c>
@@ -11300,7 +11299,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>201</v>
       </c>
@@ -11320,7 +11319,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>202</v>
       </c>
@@ -11340,7 +11339,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>203</v>
       </c>
@@ -11360,7 +11359,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>204</v>
       </c>
@@ -11380,7 +11379,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -11400,7 +11399,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>206</v>
       </c>
@@ -11420,7 +11419,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>207</v>
       </c>
@@ -11440,7 +11439,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>208</v>
       </c>
@@ -11460,7 +11459,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>209</v>
       </c>
@@ -11480,7 +11479,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>210</v>
       </c>
@@ -11500,7 +11499,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>211</v>
       </c>
@@ -11520,7 +11519,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>212</v>
       </c>
@@ -11540,7 +11539,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>213</v>
       </c>
@@ -11560,7 +11559,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>214</v>
       </c>
@@ -11580,7 +11579,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>215</v>
       </c>
@@ -11600,7 +11599,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>216</v>
       </c>
@@ -11620,7 +11619,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>217</v>
       </c>
@@ -11640,7 +11639,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>218</v>
       </c>
@@ -11660,7 +11659,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>219</v>
       </c>
@@ -11680,7 +11679,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>220</v>
       </c>
@@ -11700,7 +11699,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>221</v>
       </c>
@@ -11720,7 +11719,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -11740,7 +11739,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>223</v>
       </c>
@@ -11760,7 +11759,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>224</v>
       </c>
@@ -11780,7 +11779,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>225</v>
       </c>
@@ -11800,7 +11799,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>226</v>
       </c>
@@ -11820,7 +11819,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>227</v>
       </c>
@@ -11840,7 +11839,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>228</v>
       </c>
@@ -11860,7 +11859,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>229</v>
       </c>
@@ -11880,7 +11879,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>230</v>
       </c>
@@ -11900,7 +11899,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>231</v>
       </c>
@@ -11920,7 +11919,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>232</v>
       </c>
@@ -11940,7 +11939,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>233</v>
       </c>
@@ -11960,7 +11959,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>234</v>
       </c>
@@ -11980,7 +11979,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>235</v>
       </c>
@@ -12000,7 +11999,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>236</v>
       </c>
@@ -12020,7 +12019,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -12040,7 +12039,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>238</v>
       </c>
@@ -12060,7 +12059,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>239</v>
       </c>
@@ -12080,7 +12079,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>240</v>
       </c>
@@ -12100,7 +12099,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>241</v>
       </c>
@@ -12120,7 +12119,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>242</v>
       </c>
@@ -12140,7 +12139,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>243</v>
       </c>
@@ -12160,7 +12159,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>244</v>
       </c>
@@ -12180,7 +12179,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>245</v>
       </c>
@@ -12200,7 +12199,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>246</v>
       </c>
@@ -12220,7 +12219,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>247</v>
       </c>
@@ -12240,7 +12239,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>248</v>
       </c>
@@ -12260,7 +12259,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>249</v>
       </c>
@@ -12280,7 +12279,7 @@
         <v>1861</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>250</v>
       </c>
@@ -12300,7 +12299,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -12320,7 +12319,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>252</v>
       </c>
@@ -12340,7 +12339,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>253</v>
       </c>
@@ -12360,7 +12359,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>254</v>
       </c>
@@ -12380,7 +12379,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>255</v>
       </c>
@@ -12400,7 +12399,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>256</v>
       </c>
@@ -12420,7 +12419,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>257</v>
       </c>
@@ -12440,7 +12439,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>258</v>
       </c>
@@ -12460,7 +12459,7 @@
         <v>1870</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>259</v>
       </c>
@@ -12480,7 +12479,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>260</v>
       </c>
@@ -12500,7 +12499,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>261</v>
       </c>
@@ -12520,7 +12519,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>262</v>
       </c>
@@ -12540,7 +12539,7 @@
         <v>1874</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>263</v>
       </c>
@@ -12560,7 +12559,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>264</v>
       </c>
@@ -12580,7 +12579,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>265</v>
       </c>
@@ -12600,7 +12599,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>266</v>
       </c>
@@ -12620,7 +12619,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>267</v>
       </c>
@@ -12640,7 +12639,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>268</v>
       </c>
@@ -12660,7 +12659,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>269</v>
       </c>
@@ -12680,7 +12679,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>270</v>
       </c>
@@ -12700,7 +12699,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>271</v>
       </c>
@@ -12720,7 +12719,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>272</v>
       </c>
@@ -12740,7 +12739,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>273</v>
       </c>
@@ -12760,7 +12759,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>274</v>
       </c>
@@ -12780,7 +12779,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>275</v>
       </c>
@@ -12800,7 +12799,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>276</v>
       </c>
@@ -12820,7 +12819,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>277</v>
       </c>
@@ -12840,7 +12839,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>278</v>
       </c>
@@ -12860,7 +12859,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>244</v>
       </c>
@@ -12880,7 +12879,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>279</v>
       </c>
@@ -12900,7 +12899,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>280</v>
       </c>
@@ -12920,7 +12919,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>281</v>
       </c>
@@ -12940,7 +12939,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>282</v>
       </c>
@@ -12960,7 +12959,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>283</v>
       </c>
@@ -12980,7 +12979,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>284</v>
       </c>
@@ -13000,7 +12999,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>285</v>
       </c>
@@ -13020,7 +13019,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>286</v>
       </c>
@@ -13040,7 +13039,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>287</v>
       </c>
@@ -13048,7 +13047,7 @@
         <v>1327.77</v>
       </c>
       <c r="C284">
-        <v>-100</v>
+        <v>34.53</v>
       </c>
       <c r="D284" t="s">
         <v>597</v>
@@ -13060,7 +13059,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>288</v>
       </c>
@@ -13080,7 +13079,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>289</v>
       </c>
@@ -13100,7 +13099,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>290</v>
       </c>
@@ -13120,7 +13119,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>291</v>
       </c>
@@ -13140,7 +13139,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>292</v>
       </c>
@@ -13160,7 +13159,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>293</v>
       </c>
@@ -13180,7 +13179,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>294</v>
       </c>
@@ -13200,7 +13199,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>295</v>
       </c>
@@ -13208,7 +13207,7 @@
         <v>1322.19</v>
       </c>
       <c r="C292">
-        <v>-100</v>
+        <v>34.549999999999997</v>
       </c>
       <c r="D292" t="s">
         <v>605</v>
@@ -13220,7 +13219,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>296</v>
       </c>
@@ -13240,7 +13239,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>297</v>
       </c>
@@ -13260,7 +13259,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>298</v>
       </c>
@@ -13280,7 +13279,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>299</v>
       </c>
@@ -13300,7 +13299,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6">
       <c r="A297" t="s">
         <v>300</v>
       </c>
@@ -13320,7 +13319,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6">
       <c r="A298" t="s">
         <v>301</v>
       </c>
@@ -13340,7 +13339,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6">
       <c r="A299" t="s">
         <v>302</v>
       </c>
@@ -13360,7 +13359,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6">
       <c r="A300" t="s">
         <v>303</v>
       </c>
@@ -13380,7 +13379,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6">
       <c r="A301" t="s">
         <v>304</v>
       </c>
@@ -13400,7 +13399,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6">
       <c r="A302" t="s">
         <v>305</v>
       </c>
@@ -13420,7 +13419,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6">
       <c r="A303" t="s">
         <v>306</v>
       </c>
@@ -13440,7 +13439,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6">
       <c r="A304" t="s">
         <v>307</v>
       </c>
@@ -13460,7 +13459,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6">
       <c r="A305" t="s">
         <v>308</v>
       </c>
@@ -13480,7 +13479,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6">
       <c r="A306" t="s">
         <v>309</v>
       </c>
@@ -13500,7 +13499,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6">
       <c r="A307" t="s">
         <v>310</v>
       </c>
@@ -13520,7 +13519,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6">
       <c r="A308" t="s">
         <v>311</v>
       </c>
@@ -13540,7 +13539,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6">
       <c r="A309" t="s">
         <v>312</v>
       </c>
@@ -13560,7 +13559,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6">
       <c r="A310" t="s">
         <v>313</v>
       </c>
@@ -13580,7 +13579,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6">
       <c r="A311" t="s">
         <v>94</v>
       </c>
@@ -13600,7 +13599,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6">
       <c r="A312" t="s">
         <v>314</v>
       </c>
@@ -13620,7 +13619,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6">
       <c r="A313" t="s">
         <v>315</v>
       </c>
@@ -13640,7 +13639,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6">
       <c r="A314" t="s">
         <v>316</v>
       </c>
@@ -13660,7 +13659,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6">
       <c r="A315" t="s">
         <v>317</v>
       </c>
@@ -13680,7 +13679,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6">
       <c r="A316" t="s">
         <v>318</v>
       </c>
@@ -13700,7 +13699,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6">
       <c r="A317" t="s">
         <v>319</v>
       </c>
@@ -13720,7 +13719,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6">
       <c r="A318" t="s">
         <v>320</v>
       </c>
@@ -13740,7 +13739,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6">
       <c r="A319" t="s">
         <v>321</v>
       </c>
@@ -13760,7 +13759,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6">
       <c r="A320" t="s">
         <v>322</v>
       </c>
@@ -13780,7 +13779,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6">
       <c r="A321" t="s">
         <v>323</v>
       </c>
@@ -13800,7 +13799,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6">
       <c r="A322" t="s">
         <v>324</v>
       </c>
@@ -13820,7 +13819,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6">
       <c r="A323" t="s">
         <v>325</v>
       </c>
@@ -13828,7 +13827,7 @@
         <v>1319.18</v>
       </c>
       <c r="C323">
-        <v>-100</v>
+        <v>34.83</v>
       </c>
       <c r="D323" t="s">
         <v>621</v>
@@ -13840,7 +13839,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6">
       <c r="A324" t="s">
         <v>326</v>
       </c>
@@ -13860,7 +13859,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6">
       <c r="A325" t="s">
         <v>327</v>
       </c>
@@ -13880,7 +13879,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6">
       <c r="A326" t="s">
         <v>328</v>
       </c>
@@ -13900,7 +13899,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6">
       <c r="A327" t="s">
         <v>329</v>
       </c>
@@ -13920,7 +13919,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6">
       <c r="A328" t="s">
         <v>330</v>
       </c>
@@ -13940,7 +13939,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6">
       <c r="A329" t="s">
         <v>331</v>
       </c>
@@ -13960,7 +13959,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6">
       <c r="A330" t="s">
         <v>332</v>
       </c>
@@ -13980,7 +13979,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6">
       <c r="A331" t="s">
         <v>333</v>
       </c>
@@ -14000,7 +13999,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6">
       <c r="A332" t="s">
         <v>334</v>
       </c>
@@ -14020,7 +14019,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6">
       <c r="A333" t="s">
         <v>335</v>
       </c>
@@ -14040,7 +14039,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6">
       <c r="A334" t="s">
         <v>336</v>
       </c>
@@ -14060,7 +14059,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6">
       <c r="A335" t="s">
         <v>337</v>
       </c>
@@ -14080,7 +14079,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6">
       <c r="A336" t="s">
         <v>338</v>
       </c>
@@ -14100,7 +14099,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6">
       <c r="A337" t="s">
         <v>339</v>
       </c>
@@ -14120,7 +14119,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6">
       <c r="A338" t="s">
         <v>340</v>
       </c>
@@ -14140,7 +14139,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6">
       <c r="A339" t="s">
         <v>341</v>
       </c>
@@ -14160,7 +14159,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6">
       <c r="A340" t="s">
         <v>342</v>
       </c>
@@ -14180,7 +14179,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6">
       <c r="A341" t="s">
         <v>343</v>
       </c>
@@ -14200,7 +14199,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6">
       <c r="A342" t="s">
         <v>344</v>
       </c>
@@ -14220,7 +14219,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6">
       <c r="A343" t="s">
         <v>345</v>
       </c>
@@ -14240,7 +14239,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6">
       <c r="A344" t="s">
         <v>346</v>
       </c>
@@ -14260,7 +14259,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6">
       <c r="A345" t="s">
         <v>347</v>
       </c>
@@ -14280,7 +14279,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6">
       <c r="A346" t="s">
         <v>348</v>
       </c>
@@ -14300,7 +14299,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6">
       <c r="A347" t="s">
         <v>349</v>
       </c>
@@ -14320,7 +14319,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6">
       <c r="A348" t="s">
         <v>350</v>
       </c>
@@ -14340,7 +14339,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6">
       <c r="A349" t="s">
         <v>351</v>
       </c>
@@ -14360,7 +14359,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6">
       <c r="A350" t="s">
         <v>352</v>
       </c>
@@ -14380,7 +14379,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6">
       <c r="A351" t="s">
         <v>353</v>
       </c>
@@ -14400,7 +14399,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6">
       <c r="A352" t="s">
         <v>354</v>
       </c>
@@ -14420,7 +14419,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6">
       <c r="A353" t="s">
         <v>355</v>
       </c>
@@ -14440,7 +14439,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6">
       <c r="A354" t="s">
         <v>356</v>
       </c>
@@ -14460,7 +14459,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6">
       <c r="A355" t="s">
         <v>357</v>
       </c>
@@ -14480,7 +14479,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6">
       <c r="A356" t="s">
         <v>358</v>
       </c>
@@ -14500,7 +14499,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6">
       <c r="A357" t="s">
         <v>359</v>
       </c>
@@ -14520,7 +14519,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6">
       <c r="A358" t="s">
         <v>360</v>
       </c>
@@ -14540,7 +14539,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6">
       <c r="A359" t="s">
         <v>361</v>
       </c>
@@ -14560,7 +14559,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6">
       <c r="A360" t="s">
         <v>362</v>
       </c>
@@ -14580,7 +14579,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6">
       <c r="A361" t="s">
         <v>363</v>
       </c>
@@ -14600,7 +14599,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6">
       <c r="A362" t="s">
         <v>364</v>
       </c>
@@ -14620,7 +14619,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6">
       <c r="A363" t="s">
         <v>365</v>
       </c>
@@ -14640,7 +14639,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6">
       <c r="A364" t="s">
         <v>366</v>
       </c>
@@ -14660,7 +14659,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6">
       <c r="A365" t="s">
         <v>367</v>
       </c>
@@ -14680,7 +14679,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6">
       <c r="A366" t="s">
         <v>368</v>
       </c>
@@ -14700,7 +14699,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6">
       <c r="A367" t="s">
         <v>369</v>
       </c>
@@ -14720,7 +14719,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6">
       <c r="A368" t="s">
         <v>370</v>
       </c>
@@ -14740,7 +14739,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6">
       <c r="A369" t="s">
         <v>371</v>
       </c>
@@ -14760,7 +14759,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6">
       <c r="A370" t="s">
         <v>372</v>
       </c>
@@ -14780,7 +14779,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6">
       <c r="A371" t="s">
         <v>373</v>
       </c>
@@ -14800,7 +14799,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6">
       <c r="A372" t="s">
         <v>374</v>
       </c>
@@ -14820,7 +14819,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6">
       <c r="A373" t="s">
         <v>375</v>
       </c>
@@ -14840,7 +14839,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6">
       <c r="A374" t="s">
         <v>376</v>
       </c>
@@ -14860,7 +14859,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6">
       <c r="A375" t="s">
         <v>377</v>
       </c>
@@ -14880,7 +14879,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6">
       <c r="C376">
         <v>35.47</v>
       </c>
@@ -14894,7 +14893,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6">
       <c r="C377">
         <v>35.67</v>
       </c>
@@ -14908,7 +14907,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6">
       <c r="C378">
         <v>36.07</v>
       </c>
@@ -14922,7 +14921,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6">
       <c r="C379">
         <v>36.49</v>
       </c>
@@ -14936,7 +14935,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6">
       <c r="C380">
         <v>36.57</v>
       </c>
@@ -14950,7 +14949,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6">
       <c r="C381">
         <v>36.49</v>
       </c>
@@ -14964,7 +14963,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6">
       <c r="C382">
         <v>36.549999999999997</v>
       </c>
@@ -14978,7 +14977,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6">
       <c r="C383">
         <v>36.61</v>
       </c>
@@ -14992,7 +14991,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6">
       <c r="C384">
         <v>36.47</v>
       </c>
@@ -15006,7 +15005,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="385" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="4:6">
       <c r="D385" t="s">
         <v>677</v>
       </c>
@@ -15017,7 +15016,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="386" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="4:6">
       <c r="D386" t="s">
         <v>678</v>
       </c>
@@ -15028,7 +15027,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="387" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="4:6">
       <c r="D387" t="s">
         <v>671</v>
       </c>
@@ -15039,7 +15038,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="388" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="4:6">
       <c r="D388" t="s">
         <v>672</v>
       </c>
@@ -15050,7 +15049,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="389" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="4:6">
       <c r="D389" t="s">
         <v>673</v>
       </c>
@@ -15061,7 +15060,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="390" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="4:6">
       <c r="D390" t="s">
         <v>674</v>
       </c>
@@ -15072,7 +15071,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="391" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="4:6">
       <c r="D391" t="s">
         <v>675</v>
       </c>
@@ -15083,7 +15082,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="392" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="4:6">
       <c r="D392" t="s">
         <v>676</v>
       </c>
@@ -15094,7 +15093,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="393" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="4:6">
       <c r="D393" t="s">
         <v>677</v>
       </c>
@@ -15105,7 +15104,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="394" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="4:6">
       <c r="D394" t="s">
         <v>679</v>
       </c>
@@ -15116,7 +15115,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="395" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="4:6">
       <c r="D395" t="s">
         <v>680</v>
       </c>
@@ -15127,7 +15126,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="396" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="4:6">
       <c r="D396" t="s">
         <v>681</v>
       </c>
@@ -15138,7 +15137,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="397" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="4:6">
       <c r="D397" t="s">
         <v>682</v>
       </c>
@@ -15149,7 +15148,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="398" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="4:6">
       <c r="D398" t="s">
         <v>683</v>
       </c>
@@ -15160,7 +15159,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="399" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="4:6">
       <c r="D399" t="s">
         <v>684</v>
       </c>
@@ -15171,7 +15170,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="400" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="4:6">
       <c r="D400" t="s">
         <v>685</v>
       </c>
@@ -15182,7 +15181,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="401" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="4:6">
       <c r="D401" t="s">
         <v>686</v>
       </c>
@@ -15193,7 +15192,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="402" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="4:6">
       <c r="D402" t="s">
         <v>687</v>
       </c>
@@ -15204,7 +15203,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="403" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="4:6">
       <c r="D403" t="s">
         <v>680</v>
       </c>
@@ -15215,7 +15214,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="404" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="4:6">
       <c r="D404" t="s">
         <v>681</v>
       </c>
@@ -15226,7 +15225,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="405" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="4:6">
       <c r="D405" t="s">
         <v>682</v>
       </c>
@@ -15237,7 +15236,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="406" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="4:6">
       <c r="D406" t="s">
         <v>683</v>
       </c>
@@ -15248,7 +15247,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="407" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="4:6">
       <c r="D407" t="s">
         <v>684</v>
       </c>
@@ -15259,7 +15258,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="408" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="4:6">
       <c r="D408" t="s">
         <v>685</v>
       </c>
@@ -15270,7 +15269,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="409" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="4:6">
       <c r="D409" t="s">
         <v>686</v>
       </c>
@@ -15281,7 +15280,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="410" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="4:6">
       <c r="D410" t="s">
         <v>688</v>
       </c>
@@ -15292,7 +15291,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="411" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="4:6">
       <c r="D411" t="s">
         <v>689</v>
       </c>
@@ -15303,7 +15302,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="412" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="4:6">
       <c r="D412" t="s">
         <v>690</v>
       </c>
@@ -15314,7 +15313,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="413" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="4:6">
       <c r="D413" t="s">
         <v>691</v>
       </c>
@@ -15325,7 +15324,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="414" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="4:6">
       <c r="D414" t="s">
         <v>692</v>
       </c>
@@ -15336,7 +15335,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="415" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="4:6">
       <c r="D415" t="s">
         <v>693</v>
       </c>
@@ -15347,7 +15346,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="416" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="4:6">
       <c r="D416" t="s">
         <v>694</v>
       </c>
@@ -15358,7 +15357,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="417" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="4:6">
       <c r="D417" t="s">
         <v>695</v>
       </c>
@@ -15369,7 +15368,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="418" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="4:6">
       <c r="D418" t="s">
         <v>696</v>
       </c>
@@ -15380,7 +15379,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="419" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="4:6">
       <c r="D419" t="s">
         <v>697</v>
       </c>
@@ -15391,7 +15390,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="420" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="4:6">
       <c r="D420" t="s">
         <v>698</v>
       </c>
@@ -15402,7 +15401,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="421" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="4:6">
       <c r="D421" t="s">
         <v>699</v>
       </c>
@@ -15413,7 +15412,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="422" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="4:6">
       <c r="D422" t="s">
         <v>700</v>
       </c>
@@ -15424,7 +15423,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="423" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="4:6">
       <c r="D423" t="s">
         <v>701</v>
       </c>
@@ -15435,7 +15434,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="424" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="4:6">
       <c r="D424" t="s">
         <v>702</v>
       </c>
@@ -15446,7 +15445,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="425" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="4:6">
       <c r="D425" t="s">
         <v>703</v>
       </c>
@@ -15457,7 +15456,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="426" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="4:6">
       <c r="D426" t="s">
         <v>704</v>
       </c>
@@ -15468,7 +15467,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="427" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="4:6">
       <c r="D427" t="s">
         <v>697</v>
       </c>
@@ -15479,7 +15478,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="428" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="4:6">
       <c r="D428" t="s">
         <v>698</v>
       </c>
@@ -15490,7 +15489,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="429" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="4:6">
       <c r="D429" t="s">
         <v>699</v>
       </c>
@@ -15501,7 +15500,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="430" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="4:6">
       <c r="D430" t="s">
         <v>700</v>
       </c>
@@ -15512,7 +15511,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="431" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="4:6">
       <c r="D431" t="s">
         <v>701</v>
       </c>
@@ -15523,7 +15522,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="432" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="4:6">
       <c r="D432" t="s">
         <v>702</v>
       </c>
@@ -15534,7 +15533,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="433" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="4:6">
       <c r="D433" t="s">
         <v>703</v>
       </c>
@@ -15545,7 +15544,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="434" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="4:6">
       <c r="D434" t="s">
         <v>705</v>
       </c>
@@ -15556,7 +15555,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="435" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="4:6">
       <c r="D435" t="s">
         <v>706</v>
       </c>
@@ -15567,7 +15566,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="436" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="4:6">
       <c r="D436" t="s">
         <v>707</v>
       </c>
@@ -15578,7 +15577,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="437" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="4:6">
       <c r="D437" t="s">
         <v>708</v>
       </c>
@@ -15589,7 +15588,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="438" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="4:6">
       <c r="D438" t="s">
         <v>709</v>
       </c>
@@ -15600,7 +15599,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="439" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="4:6">
       <c r="D439" t="s">
         <v>710</v>
       </c>
@@ -15611,7 +15610,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="440" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="4:6">
       <c r="D440" t="s">
         <v>711</v>
       </c>
@@ -15622,7 +15621,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="441" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="4:6">
       <c r="D441" t="s">
         <v>712</v>
       </c>
@@ -15633,7 +15632,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="442" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="4:6">
       <c r="D442" t="s">
         <v>713</v>
       </c>
@@ -15644,7 +15643,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="443" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="4:6">
       <c r="D443" t="s">
         <v>706</v>
       </c>
@@ -15655,7 +15654,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="444" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="4:6">
       <c r="D444" t="s">
         <v>707</v>
       </c>
@@ -15666,7 +15665,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="445" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="4:6">
       <c r="D445" t="s">
         <v>708</v>
       </c>
@@ -15677,7 +15676,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="446" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="4:6">
       <c r="D446" t="s">
         <v>709</v>
       </c>
@@ -15688,7 +15687,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="447" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="4:6">
       <c r="D447" t="s">
         <v>710</v>
       </c>
@@ -15699,7 +15698,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="448" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="4:6">
       <c r="D448" t="s">
         <v>711</v>
       </c>
@@ -15710,7 +15709,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="449" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="4:6">
       <c r="D449" t="s">
         <v>712</v>
       </c>
@@ -15721,7 +15720,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="450" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="4:6">
       <c r="D450" t="s">
         <v>714</v>
       </c>
@@ -15732,7 +15731,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="451" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="4:6">
       <c r="D451" t="s">
         <v>715</v>
       </c>
@@ -15743,7 +15742,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="452" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="4:6">
       <c r="D452" t="s">
         <v>716</v>
       </c>
@@ -15754,7 +15753,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="453" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="4:6">
       <c r="D453" t="s">
         <v>717</v>
       </c>
@@ -15765,7 +15764,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="454" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="4:6">
       <c r="D454" t="s">
         <v>718</v>
       </c>
@@ -15776,7 +15775,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="455" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="4:6">
       <c r="D455" t="s">
         <v>719</v>
       </c>
@@ -15787,7 +15786,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="456" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="4:6">
       <c r="D456" t="s">
         <v>720</v>
       </c>
@@ -15798,7 +15797,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="457" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="4:6">
       <c r="D457" t="s">
         <v>721</v>
       </c>
@@ -15809,7 +15808,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="458" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="4:6">
       <c r="D458" t="s">
         <v>722</v>
       </c>
@@ -15820,7 +15819,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="459" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="4:6">
       <c r="D459" t="s">
         <v>723</v>
       </c>
@@ -15831,7 +15830,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="460" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="4:6">
       <c r="D460" t="s">
         <v>724</v>
       </c>
@@ -15842,7 +15841,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="461" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="4:6">
       <c r="D461" t="s">
         <v>725</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="462" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="4:6">
       <c r="D462" t="s">
         <v>726</v>
       </c>
@@ -15864,7 +15863,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="463" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="4:6">
       <c r="D463" t="s">
         <v>727</v>
       </c>
@@ -15875,7 +15874,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="464" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="4:6">
       <c r="D464" t="s">
         <v>728</v>
       </c>
@@ -15886,7 +15885,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="465" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="4:6">
       <c r="D465" t="s">
         <v>729</v>
       </c>
@@ -15897,7 +15896,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="466" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="4:6">
       <c r="D466" t="s">
         <v>730</v>
       </c>
@@ -15908,7 +15907,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="467" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="4:6">
       <c r="D467" t="s">
         <v>731</v>
       </c>
@@ -15919,7 +15918,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="468" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="4:6">
       <c r="D468" t="s">
         <v>732</v>
       </c>
@@ -15930,7 +15929,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="469" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="4:6">
       <c r="D469" t="s">
         <v>733</v>
       </c>
@@ -15941,7 +15940,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="470" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="4:6">
       <c r="D470" t="s">
         <v>734</v>
       </c>
@@ -15952,7 +15951,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="471" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="4:6">
       <c r="D471" t="s">
         <v>735</v>
       </c>
@@ -15963,7 +15962,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="472" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="4:6">
       <c r="D472" t="s">
         <v>736</v>
       </c>
@@ -15974,7 +15973,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="473" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="4:6">
       <c r="D473" t="s">
         <v>737</v>
       </c>
@@ -15985,7 +15984,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="474" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="4:6">
       <c r="D474" t="s">
         <v>738</v>
       </c>
@@ -15996,7 +15995,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="475" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="4:6">
       <c r="D475" t="s">
         <v>731</v>
       </c>
@@ -16007,7 +16006,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="476" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="4:6">
       <c r="D476" t="s">
         <v>732</v>
       </c>
@@ -16018,7 +16017,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="477" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="4:6">
       <c r="D477" t="s">
         <v>733</v>
       </c>
@@ -16029,7 +16028,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="478" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="4:6">
       <c r="D478" t="s">
         <v>734</v>
       </c>
@@ -16040,7 +16039,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="479" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="4:6">
       <c r="D479" t="s">
         <v>735</v>
       </c>
@@ -16051,7 +16050,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="480" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="4:6">
       <c r="D480" t="s">
         <v>736</v>
       </c>
@@ -16062,7 +16061,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="481" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="4:6">
       <c r="D481" t="s">
         <v>737</v>
       </c>
@@ -16073,7 +16072,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="482" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="4:6">
       <c r="D482" t="s">
         <v>739</v>
       </c>
@@ -16084,7 +16083,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="483" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="4:6">
       <c r="D483" t="s">
         <v>740</v>
       </c>
@@ -16095,7 +16094,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="484" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="4:6">
       <c r="D484" t="s">
         <v>741</v>
       </c>
@@ -16106,7 +16105,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="485" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="4:6">
       <c r="D485" t="s">
         <v>742</v>
       </c>
@@ -16117,7 +16116,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="486" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="4:6">
       <c r="D486" t="s">
         <v>743</v>
       </c>
@@ -16128,7 +16127,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="487" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="4:6">
       <c r="D487" t="s">
         <v>744</v>
       </c>
@@ -16139,7 +16138,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="488" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="4:6">
       <c r="D488" t="s">
         <v>745</v>
       </c>
@@ -16150,7 +16149,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="489" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="4:6">
       <c r="D489" t="s">
         <v>746</v>
       </c>
@@ -16161,7 +16160,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="490" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="4:6">
       <c r="D490" t="s">
         <v>747</v>
       </c>
@@ -16172,7 +16171,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="491" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="4:6">
       <c r="D491" t="s">
         <v>748</v>
       </c>
@@ -16183,7 +16182,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="492" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="4:6">
       <c r="D492" t="s">
         <v>749</v>
       </c>
@@ -16194,7 +16193,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="493" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="4:6">
       <c r="D493" t="s">
         <v>750</v>
       </c>
@@ -16205,7 +16204,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="494" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="4:6">
       <c r="D494" t="s">
         <v>751</v>
       </c>
@@ -16216,7 +16215,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="495" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="4:6">
       <c r="D495" t="s">
         <v>752</v>
       </c>
@@ -16227,7 +16226,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="496" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="4:6">
       <c r="D496" t="s">
         <v>753</v>
       </c>
@@ -16238,7 +16237,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="497" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="4:6">
       <c r="D497" t="s">
         <v>754</v>
       </c>
@@ -16249,7 +16248,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="498" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="4:6">
       <c r="D498" t="s">
         <v>755</v>
       </c>
@@ -16260,7 +16259,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="499" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="4:6">
       <c r="D499" t="s">
         <v>756</v>
       </c>
@@ -16271,7 +16270,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="500" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="4:6">
       <c r="D500" t="s">
         <v>757</v>
       </c>
@@ -16282,7 +16281,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="501" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="4:6">
       <c r="D501" t="s">
         <v>758</v>
       </c>
@@ -16293,7 +16292,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="502" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="4:6">
       <c r="D502" t="s">
         <v>759</v>
       </c>
@@ -16304,7 +16303,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="503" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="4:6">
       <c r="D503" t="s">
         <v>760</v>
       </c>
@@ -16315,7 +16314,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="504" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="4:6">
       <c r="D504" t="s">
         <v>761</v>
       </c>
@@ -16326,7 +16325,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="505" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="4:6">
       <c r="D505" t="s">
         <v>762</v>
       </c>
@@ -16337,7 +16336,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="506" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="4:6">
       <c r="D506" t="s">
         <v>763</v>
       </c>
@@ -16348,7 +16347,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="507" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="4:6">
       <c r="D507" t="s">
         <v>764</v>
       </c>
@@ -16359,7 +16358,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="508" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="4:6">
       <c r="D508" t="s">
         <v>765</v>
       </c>
@@ -16370,7 +16369,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="509" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="4:6">
       <c r="D509" t="s">
         <v>766</v>
       </c>
@@ -16381,7 +16380,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="510" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="4:6">
       <c r="D510" t="s">
         <v>767</v>
       </c>
@@ -16392,7 +16391,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="511" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="4:6">
       <c r="D511" t="s">
         <v>768</v>
       </c>
@@ -16403,7 +16402,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="512" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="4:6">
       <c r="D512" t="s">
         <v>769</v>
       </c>
@@ -16414,7 +16413,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="513" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="4:6">
       <c r="D513" t="s">
         <v>770</v>
       </c>
@@ -16425,7 +16424,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="514" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="4:6">
       <c r="D514" t="s">
         <v>771</v>
       </c>
@@ -16436,7 +16435,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="515" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="4:6">
       <c r="D515" t="s">
         <v>772</v>
       </c>
@@ -16447,7 +16446,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="516" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="4:6">
       <c r="D516" t="s">
         <v>773</v>
       </c>
@@ -16458,7 +16457,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="517" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="4:6">
       <c r="D517" t="s">
         <v>774</v>
       </c>
@@ -16469,7 +16468,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="518" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="4:6">
       <c r="D518" t="s">
         <v>775</v>
       </c>
@@ -16480,7 +16479,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="519" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="4:6">
       <c r="D519" t="s">
         <v>776</v>
       </c>
@@ -16491,7 +16490,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="520" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="4:6">
       <c r="D520" t="s">
         <v>777</v>
       </c>
@@ -16502,7 +16501,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="521" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="4:6">
       <c r="D521" t="s">
         <v>778</v>
       </c>
@@ -16513,7 +16512,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="522" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="4:6">
       <c r="D522" t="s">
         <v>779</v>
       </c>
@@ -16524,7 +16523,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="523" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="4:6">
       <c r="D523" t="s">
         <v>780</v>
       </c>
@@ -16535,7 +16534,7 @@
         <v>2076</v>
       </c>
     </row>
-    <row r="524" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="4:6">
       <c r="D524" t="s">
         <v>781</v>
       </c>
@@ -16546,7 +16545,7 @@
         <v>2077</v>
       </c>
     </row>
-    <row r="525" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="4:6">
       <c r="D525" t="s">
         <v>782</v>
       </c>
@@ -16557,7 +16556,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="526" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="4:6">
       <c r="D526" t="s">
         <v>783</v>
       </c>
@@ -16568,7 +16567,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="527" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="4:6">
       <c r="D527" t="s">
         <v>784</v>
       </c>
@@ -16579,7 +16578,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="528" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="4:6">
       <c r="D528" t="s">
         <v>785</v>
       </c>
@@ -16590,7 +16589,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="529" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="4:6">
       <c r="D529" t="s">
         <v>786</v>
       </c>
@@ -16601,7 +16600,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="530" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="530" spans="4:6">
       <c r="D530" t="s">
         <v>787</v>
       </c>
@@ -16612,7 +16611,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="531" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="4:6">
       <c r="D531" t="s">
         <v>788</v>
       </c>
@@ -16623,7 +16622,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="532" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="4:6">
       <c r="D532" t="s">
         <v>789</v>
       </c>
@@ -16634,7 +16633,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="533" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="4:6">
       <c r="D533" t="s">
         <v>790</v>
       </c>
@@ -16645,7 +16644,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="534" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="4:6">
       <c r="D534" t="s">
         <v>791</v>
       </c>
@@ -16656,7 +16655,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="535" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="4:6">
       <c r="D535" t="s">
         <v>792</v>
       </c>
@@ -16667,7 +16666,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="536" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="4:6">
       <c r="D536" t="s">
         <v>793</v>
       </c>
@@ -16678,7 +16677,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="537" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="4:6">
       <c r="D537" t="s">
         <v>794</v>
       </c>
@@ -16689,7 +16688,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="538" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="538" spans="4:6">
       <c r="D538" t="s">
         <v>795</v>
       </c>
@@ -16700,7 +16699,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="539" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="4:6">
       <c r="D539" t="s">
         <v>796</v>
       </c>
@@ -16711,7 +16710,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="540" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="4:6">
       <c r="D540" t="s">
         <v>797</v>
       </c>
@@ -16722,7 +16721,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="541" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="4:6">
       <c r="D541" t="s">
         <v>798</v>
       </c>
@@ -16733,7 +16732,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="542" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="4:6">
       <c r="D542" t="s">
         <v>799</v>
       </c>
@@ -16744,7 +16743,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="543" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="4:6">
       <c r="D543" t="s">
         <v>800</v>
       </c>
@@ -16755,7 +16754,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="544" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="4:6">
       <c r="D544" t="s">
         <v>801</v>
       </c>
@@ -16766,7 +16765,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="545" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="545" spans="4:6">
       <c r="D545" t="s">
         <v>802</v>
       </c>
@@ -16777,7 +16776,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="546" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="546" spans="4:6">
       <c r="D546" t="s">
         <v>803</v>
       </c>
@@ -16788,7 +16787,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="547" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="547" spans="4:6">
       <c r="D547" t="s">
         <v>796</v>
       </c>
@@ -16799,7 +16798,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="548" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="548" spans="4:6">
       <c r="D548" t="s">
         <v>797</v>
       </c>
@@ -16810,7 +16809,7 @@
         <v>2093</v>
       </c>
     </row>
-    <row r="549" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="549" spans="4:6">
       <c r="D549" t="s">
         <v>798</v>
       </c>
@@ -16821,7 +16820,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="550" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="550" spans="4:6">
       <c r="D550" t="s">
         <v>799</v>
       </c>
@@ -16832,7 +16831,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="551" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="551" spans="4:6">
       <c r="D551" t="s">
         <v>800</v>
       </c>
@@ -16843,7 +16842,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="552" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="552" spans="4:6">
       <c r="D552" t="s">
         <v>801</v>
       </c>
@@ -16854,7 +16853,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="553" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="553" spans="4:6">
       <c r="D553" t="s">
         <v>802</v>
       </c>
@@ -16865,7 +16864,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="554" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="554" spans="4:6">
       <c r="D554" t="s">
         <v>804</v>
       </c>
@@ -16876,7 +16875,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="555" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="555" spans="4:6">
       <c r="D555" t="s">
         <v>805</v>
       </c>
@@ -16887,7 +16886,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="556" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="556" spans="4:6">
       <c r="D556" t="s">
         <v>806</v>
       </c>
@@ -16898,7 +16897,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="557" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="557" spans="4:6">
       <c r="D557" t="s">
         <v>807</v>
       </c>
@@ -16909,7 +16908,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="558" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="558" spans="4:6">
       <c r="D558" t="s">
         <v>808</v>
       </c>
@@ -16920,7 +16919,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="559" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="559" spans="4:6">
       <c r="D559" t="s">
         <v>809</v>
       </c>
@@ -16931,7 +16930,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="560" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="560" spans="4:6">
       <c r="D560" t="s">
         <v>810</v>
       </c>
@@ -16942,7 +16941,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="561" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="561" spans="4:6">
       <c r="D561" t="s">
         <v>811</v>
       </c>
@@ -16953,7 +16952,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="562" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="562" spans="4:6">
       <c r="D562" t="s">
         <v>812</v>
       </c>
@@ -16964,7 +16963,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="563" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="563" spans="4:6">
       <c r="D563" t="s">
         <v>805</v>
       </c>
@@ -16975,7 +16974,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="564" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="564" spans="4:6">
       <c r="D564" t="s">
         <v>806</v>
       </c>
@@ -16986,7 +16985,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="565" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="565" spans="4:6">
       <c r="D565" t="s">
         <v>807</v>
       </c>
@@ -16997,7 +16996,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="566" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="566" spans="4:6">
       <c r="D566" t="s">
         <v>808</v>
       </c>
@@ -17008,7 +17007,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="567" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="567" spans="4:6">
       <c r="D567" t="s">
         <v>809</v>
       </c>
@@ -17019,7 +17018,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="568" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="568" spans="4:6">
       <c r="D568" t="s">
         <v>810</v>
       </c>
@@ -17030,7 +17029,7 @@
         <v>2106</v>
       </c>
     </row>
-    <row r="569" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="569" spans="4:6">
       <c r="D569" t="s">
         <v>811</v>
       </c>
@@ -17041,7 +17040,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="570" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="570" spans="4:6">
       <c r="D570" t="s">
         <v>813</v>
       </c>
@@ -17052,7 +17051,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="571" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="571" spans="4:6">
       <c r="D571" t="s">
         <v>814</v>
       </c>
@@ -17063,7 +17062,7 @@
         <v>2110</v>
       </c>
     </row>
-    <row r="572" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="572" spans="4:6">
       <c r="D572" t="s">
         <v>815</v>
       </c>
@@ -17074,7 +17073,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="573" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="573" spans="4:6">
       <c r="D573" t="s">
         <v>816</v>
       </c>
@@ -17085,7 +17084,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="574" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="574" spans="4:6">
       <c r="D574" t="s">
         <v>817</v>
       </c>
@@ -17096,7 +17095,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="575" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="575" spans="4:6">
       <c r="D575" t="s">
         <v>818</v>
       </c>
@@ -17107,7 +17106,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="576" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="576" spans="4:6">
       <c r="D576" t="s">
         <v>819</v>
       </c>
@@ -17118,7 +17117,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="577" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="4:6">
       <c r="D577" t="s">
         <v>820</v>
       </c>
@@ -17129,7 +17128,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="578" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="4:6">
       <c r="D578" t="s">
         <v>821</v>
       </c>
@@ -17140,7 +17139,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="579" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="4:6">
       <c r="D579" t="s">
         <v>822</v>
       </c>
@@ -17151,7 +17150,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="580" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="4:6">
       <c r="D580" t="s">
         <v>823</v>
       </c>
@@ -17162,7 +17161,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="581" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="4:6">
       <c r="D581" t="s">
         <v>824</v>
       </c>
@@ -17173,7 +17172,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="582" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="4:6">
       <c r="D582" t="s">
         <v>825</v>
       </c>
@@ -17184,7 +17183,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="583" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="4:6">
       <c r="D583" t="s">
         <v>826</v>
       </c>
@@ -17195,7 +17194,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="584" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="4:6">
       <c r="D584" t="s">
         <v>827</v>
       </c>
@@ -17206,7 +17205,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="585" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="4:6">
       <c r="D585" t="s">
         <v>828</v>
       </c>
@@ -17217,7 +17216,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="586" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="4:6">
       <c r="D586" t="s">
         <v>829</v>
       </c>
@@ -17228,7 +17227,7 @@
         <v>2125</v>
       </c>
     </row>
-    <row r="587" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="4:6">
       <c r="D587" t="s">
         <v>830</v>
       </c>
@@ -17239,7 +17238,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="588" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="4:6">
       <c r="D588" t="s">
         <v>831</v>
       </c>
@@ -17250,7 +17249,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="589" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="4:6">
       <c r="D589" t="s">
         <v>832</v>
       </c>
@@ -17261,7 +17260,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="590" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="4:6">
       <c r="D590" t="s">
         <v>833</v>
       </c>
@@ -17272,7 +17271,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="591" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="4:6">
       <c r="D591" t="s">
         <v>834</v>
       </c>
@@ -17283,7 +17282,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="592" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="4:6">
       <c r="D592" t="s">
         <v>835</v>
       </c>
@@ -17294,7 +17293,7 @@
         <v>2131</v>
       </c>
     </row>
-    <row r="593" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="4:6">
       <c r="D593" t="s">
         <v>836</v>
       </c>
@@ -17305,7 +17304,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="594" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="4:6">
       <c r="D594" t="s">
         <v>837</v>
       </c>
@@ -17316,7 +17315,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="595" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="4:6">
       <c r="D595" t="s">
         <v>838</v>
       </c>
@@ -17327,7 +17326,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="596" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="4:6">
       <c r="D596" t="s">
         <v>839</v>
       </c>
@@ -17338,7 +17337,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="597" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="4:6">
       <c r="D597" t="s">
         <v>840</v>
       </c>
@@ -17349,7 +17348,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="598" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="4:6">
       <c r="D598" t="s">
         <v>841</v>
       </c>
@@ -17360,7 +17359,7 @@
         <v>2137</v>
       </c>
     </row>
-    <row r="599" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="4:6">
       <c r="D599" t="s">
         <v>842</v>
       </c>
@@ -17371,7 +17370,7 @@
         <v>2138</v>
       </c>
     </row>
-    <row r="600" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="4:6">
       <c r="D600" t="s">
         <v>843</v>
       </c>
@@ -17382,7 +17381,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="601" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="4:6">
       <c r="D601" t="s">
         <v>844</v>
       </c>
@@ -17393,7 +17392,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="602" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="4:6">
       <c r="D602" t="s">
         <v>845</v>
       </c>
@@ -17404,7 +17403,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="603" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="4:6">
       <c r="D603" t="s">
         <v>846</v>
       </c>
@@ -17415,7 +17414,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="604" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="4:6">
       <c r="D604" t="s">
         <v>847</v>
       </c>
@@ -17426,7 +17425,7 @@
         <v>2143</v>
       </c>
     </row>
-    <row r="605" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="4:6">
       <c r="D605" t="s">
         <v>848</v>
       </c>
@@ -17437,7 +17436,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="606" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="4:6">
       <c r="D606" t="s">
         <v>849</v>
       </c>
@@ -17448,7 +17447,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="607" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="4:6">
       <c r="D607" t="s">
         <v>850</v>
       </c>
@@ -17459,7 +17458,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="608" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="4:6">
       <c r="D608" t="s">
         <v>851</v>
       </c>
@@ -17470,7 +17469,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="609" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="4:6">
       <c r="D609" t="s">
         <v>852</v>
       </c>
@@ -17481,7 +17480,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="610" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="4:6">
       <c r="D610" t="s">
         <v>853</v>
       </c>
@@ -17492,7 +17491,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="611" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="4:6">
       <c r="D611" t="s">
         <v>854</v>
       </c>
@@ -17503,7 +17502,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="612" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="4:6">
       <c r="D612" t="s">
         <v>855</v>
       </c>
@@ -17514,7 +17513,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="613" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="4:6">
       <c r="D613" t="s">
         <v>856</v>
       </c>
@@ -17525,7 +17524,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="614" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="4:6">
       <c r="D614" t="s">
         <v>857</v>
       </c>
@@ -17536,7 +17535,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="615" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="4:6">
       <c r="D615" t="s">
         <v>858</v>
       </c>
@@ -17547,7 +17546,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="616" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="4:6">
       <c r="D616" t="s">
         <v>859</v>
       </c>
@@ -17558,7 +17557,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="617" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="4:6">
       <c r="D617" t="s">
         <v>860</v>
       </c>
@@ -17569,7 +17568,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="618" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="4:6">
       <c r="D618" t="s">
         <v>861</v>
       </c>
@@ -17580,7 +17579,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="619" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="4:6">
       <c r="D619" t="s">
         <v>854</v>
       </c>
@@ -17591,7 +17590,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="620" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="4:6">
       <c r="D620" t="s">
         <v>855</v>
       </c>
@@ -17602,7 +17601,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="621" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="4:6">
       <c r="D621" t="s">
         <v>856</v>
       </c>
@@ -17613,7 +17612,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="622" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="4:6">
       <c r="D622" t="s">
         <v>857</v>
       </c>
@@ -17624,7 +17623,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="623" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="4:6">
       <c r="D623" t="s">
         <v>858</v>
       </c>
@@ -17635,7 +17634,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="624" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="4:6">
       <c r="D624" t="s">
         <v>859</v>
       </c>
@@ -17646,7 +17645,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="625" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="4:6">
       <c r="D625" t="s">
         <v>860</v>
       </c>
@@ -17657,7 +17656,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="626" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="4:6">
       <c r="D626" t="s">
         <v>862</v>
       </c>
@@ -17668,7 +17667,7 @@
         <v>2158</v>
       </c>
     </row>
-    <row r="627" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="4:6">
       <c r="D627" t="s">
         <v>863</v>
       </c>
@@ -17679,7 +17678,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="628" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="4:6">
       <c r="D628" t="s">
         <v>864</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="629" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="4:6">
       <c r="D629" t="s">
         <v>865</v>
       </c>
@@ -17701,7 +17700,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="630" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="4:6">
       <c r="D630" t="s">
         <v>866</v>
       </c>
@@ -17712,7 +17711,7 @@
         <v>2162</v>
       </c>
     </row>
-    <row r="631" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="4:6">
       <c r="D631" t="s">
         <v>867</v>
       </c>
@@ -17723,7 +17722,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="632" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="4:6">
       <c r="D632" t="s">
         <v>868</v>
       </c>
@@ -17734,7 +17733,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="633" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="4:6">
       <c r="D633" t="s">
         <v>869</v>
       </c>
@@ -17745,7 +17744,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="634" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="4:6">
       <c r="D634" t="s">
         <v>870</v>
       </c>
@@ -17756,7 +17755,7 @@
         <v>2166</v>
       </c>
     </row>
-    <row r="635" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="4:6">
       <c r="D635" t="s">
         <v>871</v>
       </c>
@@ -17767,7 +17766,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="636" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="4:6">
       <c r="D636" t="s">
         <v>872</v>
       </c>
@@ -17778,7 +17777,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="637" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="4:6">
       <c r="D637" t="s">
         <v>873</v>
       </c>
@@ -17789,7 +17788,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="638" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="4:6">
       <c r="D638" t="s">
         <v>874</v>
       </c>
@@ -17800,7 +17799,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="639" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="4:6">
       <c r="D639" t="s">
         <v>875</v>
       </c>
@@ -17811,7 +17810,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="640" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="4:6">
       <c r="D640" t="s">
         <v>876</v>
       </c>
@@ -17822,7 +17821,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="641" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="4:6">
       <c r="D641" t="s">
         <v>877</v>
       </c>
@@ -17833,7 +17832,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="642" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="4:6">
       <c r="D642" t="s">
         <v>878</v>
       </c>
@@ -17844,7 +17843,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="643" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="4:6">
       <c r="D643" t="s">
         <v>871</v>
       </c>
@@ -17855,7 +17854,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="644" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="4:6">
       <c r="D644" t="s">
         <v>872</v>
       </c>
@@ -17866,7 +17865,7 @@
         <v>2168</v>
       </c>
     </row>
-    <row r="645" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="4:6">
       <c r="D645" t="s">
         <v>873</v>
       </c>
@@ -17877,7 +17876,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="646" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="4:6">
       <c r="D646" t="s">
         <v>874</v>
       </c>
@@ -17888,7 +17887,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="647" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="4:6">
       <c r="D647" t="s">
         <v>875</v>
       </c>
@@ -17899,7 +17898,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="648" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="648" spans="4:6">
       <c r="D648" t="s">
         <v>876</v>
       </c>
@@ -17910,7 +17909,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="649" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="649" spans="4:6">
       <c r="D649" t="s">
         <v>877</v>
       </c>
@@ -17921,7 +17920,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="650" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="650" spans="4:6">
       <c r="D650" t="s">
         <v>879</v>
       </c>
@@ -17932,7 +17931,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="651" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="651" spans="4:6">
       <c r="D651" t="s">
         <v>880</v>
       </c>
@@ -17943,7 +17942,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="652" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="652" spans="4:6">
       <c r="D652" t="s">
         <v>881</v>
       </c>
@@ -17954,7 +17953,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="653" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="653" spans="4:6">
       <c r="D653" t="s">
         <v>882</v>
       </c>
@@ -17965,7 +17964,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="654" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="654" spans="4:6">
       <c r="D654" t="s">
         <v>883</v>
       </c>
@@ -17976,7 +17975,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="655" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="655" spans="4:6">
       <c r="D655" t="s">
         <v>884</v>
       </c>
@@ -17987,7 +17986,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="656" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="656" spans="4:6">
       <c r="D656" t="s">
         <v>885</v>
       </c>
@@ -17998,7 +17997,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="657" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="657" spans="4:6">
       <c r="D657" t="s">
         <v>886</v>
       </c>
@@ -18009,7 +18008,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="658" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="658" spans="4:6">
       <c r="D658" t="s">
         <v>887</v>
       </c>
@@ -18020,7 +18019,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="659" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="659" spans="4:6">
       <c r="D659" t="s">
         <v>888</v>
       </c>
@@ -18031,7 +18030,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="660" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="660" spans="4:6">
       <c r="D660" t="s">
         <v>889</v>
       </c>
@@ -18042,7 +18041,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="661" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="661" spans="4:6">
       <c r="D661" t="s">
         <v>890</v>
       </c>
@@ -18053,7 +18052,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="662" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="662" spans="4:6">
       <c r="D662" t="s">
         <v>891</v>
       </c>
@@ -18064,7 +18063,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="663" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="663" spans="4:6">
       <c r="D663" t="s">
         <v>892</v>
       </c>
@@ -18075,7 +18074,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="664" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="664" spans="4:6">
       <c r="D664" t="s">
         <v>893</v>
       </c>
@@ -18086,7 +18085,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="665" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="665" spans="4:6">
       <c r="D665" t="s">
         <v>894</v>
       </c>
@@ -18097,7 +18096,7 @@
         <v>2190</v>
       </c>
     </row>
-    <row r="666" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="666" spans="4:6">
       <c r="D666" t="s">
         <v>895</v>
       </c>
@@ -18108,7 +18107,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="667" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="667" spans="4:6">
       <c r="D667" t="s">
         <v>896</v>
       </c>
@@ -18119,7 +18118,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="668" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="668" spans="4:6">
       <c r="D668" t="s">
         <v>897</v>
       </c>
@@ -18130,7 +18129,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="669" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="669" spans="4:6">
       <c r="D669" t="s">
         <v>898</v>
       </c>
@@ -18141,7 +18140,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="670" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="670" spans="4:6">
       <c r="D670" t="s">
         <v>899</v>
       </c>
@@ -18152,7 +18151,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="671" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="671" spans="4:6">
       <c r="D671" t="s">
         <v>900</v>
       </c>
@@ -18163,7 +18162,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="672" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="672" spans="4:6">
       <c r="D672" t="s">
         <v>901</v>
       </c>
@@ -18174,7 +18173,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="673" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="673" spans="4:6">
       <c r="D673" t="s">
         <v>902</v>
       </c>
@@ -18185,7 +18184,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="674" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="674" spans="4:6">
       <c r="D674" t="s">
         <v>903</v>
       </c>
@@ -18196,7 +18195,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="675" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="675" spans="4:6">
       <c r="D675" t="s">
         <v>904</v>
       </c>
@@ -18207,7 +18206,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="676" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="676" spans="4:6">
       <c r="D676" t="s">
         <v>905</v>
       </c>
@@ -18218,7 +18217,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="677" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="677" spans="4:6">
       <c r="D677" t="s">
         <v>906</v>
       </c>
@@ -18229,7 +18228,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="678" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="678" spans="4:6">
       <c r="D678" t="s">
         <v>907</v>
       </c>
@@ -18240,7 +18239,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="679" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="679" spans="4:6">
       <c r="D679" t="s">
         <v>908</v>
       </c>
@@ -18251,7 +18250,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="680" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="680" spans="4:6">
       <c r="D680" t="s">
         <v>909</v>
       </c>
@@ -18262,7 +18261,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="681" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="681" spans="4:6">
       <c r="D681" t="s">
         <v>910</v>
       </c>
@@ -18273,7 +18272,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="682" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="682" spans="4:6">
       <c r="D682" t="s">
         <v>911</v>
       </c>
@@ -18284,7 +18283,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="683" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="683" spans="4:6">
       <c r="D683" t="s">
         <v>912</v>
       </c>
@@ -18295,7 +18294,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="684" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="684" spans="4:6">
       <c r="D684" t="s">
         <v>913</v>
       </c>
@@ -18306,7 +18305,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="685" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="685" spans="4:6">
       <c r="D685" t="s">
         <v>914</v>
       </c>
@@ -18317,7 +18316,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="686" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="686" spans="4:6">
       <c r="D686" t="s">
         <v>915</v>
       </c>
@@ -18328,7 +18327,7 @@
         <v>2211</v>
       </c>
     </row>
-    <row r="687" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="687" spans="4:6">
       <c r="D687" t="s">
         <v>916</v>
       </c>
@@ -18339,7 +18338,7 @@
         <v>2212</v>
       </c>
     </row>
-    <row r="688" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="688" spans="4:6">
       <c r="D688" t="s">
         <v>917</v>
       </c>
@@ -18350,7 +18349,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="689" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="689" spans="4:6">
       <c r="D689" t="s">
         <v>918</v>
       </c>
@@ -18361,7 +18360,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="690" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="690" spans="4:6">
       <c r="D690" t="s">
         <v>919</v>
       </c>
@@ -18372,7 +18371,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="691" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="691" spans="4:6">
       <c r="D691" t="s">
         <v>920</v>
       </c>
@@ -18383,7 +18382,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="692" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="692" spans="4:6">
       <c r="D692" t="s">
         <v>921</v>
       </c>
@@ -18394,7 +18393,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="693" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="693" spans="4:6">
       <c r="D693" t="s">
         <v>922</v>
       </c>
@@ -18405,7 +18404,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="694" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="694" spans="4:6">
       <c r="D694" t="s">
         <v>923</v>
       </c>
@@ -18416,7 +18415,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="695" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="695" spans="4:6">
       <c r="D695" t="s">
         <v>924</v>
       </c>
@@ -18427,7 +18426,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="696" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="696" spans="4:6">
       <c r="D696" t="s">
         <v>925</v>
       </c>
@@ -18438,7 +18437,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="697" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="697" spans="4:6">
       <c r="D697" t="s">
         <v>926</v>
       </c>
@@ -18449,7 +18448,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="698" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="698" spans="4:6">
       <c r="D698" t="s">
         <v>927</v>
       </c>
@@ -18460,7 +18459,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="699" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="699" spans="4:6">
       <c r="D699" t="s">
         <v>928</v>
       </c>
@@ -18471,7 +18470,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="700" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="700" spans="4:6">
       <c r="D700" t="s">
         <v>929</v>
       </c>
@@ -18482,7 +18481,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="701" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="701" spans="4:6">
       <c r="D701" t="s">
         <v>930</v>
       </c>
@@ -18493,7 +18492,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="702" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="702" spans="4:6">
       <c r="D702" t="s">
         <v>931</v>
       </c>
@@ -18504,7 +18503,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="703" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="703" spans="4:6">
       <c r="D703" t="s">
         <v>932</v>
       </c>
@@ -18515,7 +18514,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="704" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="704" spans="4:6">
       <c r="D704" t="s">
         <v>933</v>
       </c>
@@ -18526,7 +18525,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="705" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="705" spans="4:6">
       <c r="D705" t="s">
         <v>934</v>
       </c>
@@ -18537,7 +18536,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="706" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="706" spans="4:6">
       <c r="D706" t="s">
         <v>935</v>
       </c>
@@ -18548,7 +18547,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="707" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="707" spans="4:6">
       <c r="D707" t="s">
         <v>936</v>
       </c>
@@ -18559,7 +18558,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="708" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="708" spans="4:6">
       <c r="D708" t="s">
         <v>937</v>
       </c>
@@ -18570,7 +18569,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="709" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="709" spans="4:6">
       <c r="D709" t="s">
         <v>938</v>
       </c>
@@ -18581,7 +18580,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="710" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="710" spans="4:6">
       <c r="D710" t="s">
         <v>939</v>
       </c>
@@ -18592,7 +18591,7 @@
         <v>2235</v>
       </c>
     </row>
-    <row r="711" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="711" spans="4:6">
       <c r="D711" t="s">
         <v>940</v>
       </c>
@@ -18603,7 +18602,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="712" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="712" spans="4:6">
       <c r="D712" t="s">
         <v>941</v>
       </c>
@@ -18614,7 +18613,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="713" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="713" spans="4:6">
       <c r="D713" t="s">
         <v>942</v>
       </c>
@@ -18625,7 +18624,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="714" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="714" spans="4:6">
       <c r="D714" t="s">
         <v>943</v>
       </c>
@@ -18636,7 +18635,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="715" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="715" spans="4:6">
       <c r="D715" t="s">
         <v>944</v>
       </c>
@@ -18647,7 +18646,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="716" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="716" spans="4:6">
       <c r="D716" t="s">
         <v>945</v>
       </c>
@@ -18658,7 +18657,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="717" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="717" spans="4:6">
       <c r="D717" t="s">
         <v>946</v>
       </c>
@@ -18669,7 +18668,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="718" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="718" spans="4:6">
       <c r="D718" t="s">
         <v>947</v>
       </c>
@@ -18680,7 +18679,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="719" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="719" spans="4:6">
       <c r="D719" t="s">
         <v>948</v>
       </c>
@@ -18691,7 +18690,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="720" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="720" spans="4:6">
       <c r="D720" t="s">
         <v>949</v>
       </c>
@@ -18702,7 +18701,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="721" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="721" spans="4:6">
       <c r="D721" t="s">
         <v>950</v>
       </c>
@@ -18713,7 +18712,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="722" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="722" spans="4:6">
       <c r="D722" t="s">
         <v>951</v>
       </c>
@@ -18724,7 +18723,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="723" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="723" spans="4:6">
       <c r="D723" t="s">
         <v>944</v>
       </c>
@@ -18735,7 +18734,7 @@
         <v>2240</v>
       </c>
     </row>
-    <row r="724" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="724" spans="4:6">
       <c r="D724" t="s">
         <v>945</v>
       </c>
@@ -18746,7 +18745,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="725" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="725" spans="4:6">
       <c r="D725" t="s">
         <v>946</v>
       </c>
@@ -18757,7 +18756,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="726" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="726" spans="4:6">
       <c r="D726" t="s">
         <v>947</v>
       </c>
@@ -18768,7 +18767,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="727" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="727" spans="4:6">
       <c r="D727" t="s">
         <v>948</v>
       </c>
@@ -18779,7 +18778,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="728" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="728" spans="4:6">
       <c r="D728" t="s">
         <v>949</v>
       </c>
@@ -18790,7 +18789,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="729" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="729" spans="4:6">
       <c r="D729" t="s">
         <v>950</v>
       </c>
@@ -18801,7 +18800,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="730" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="730" spans="4:6">
       <c r="D730" t="s">
         <v>952</v>
       </c>
@@ -18812,7 +18811,7 @@
         <v>2248</v>
       </c>
     </row>
-    <row r="731" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="731" spans="4:6">
       <c r="D731" t="s">
         <v>953</v>
       </c>
@@ -18823,7 +18822,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="732" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="732" spans="4:6">
       <c r="D732" t="s">
         <v>954</v>
       </c>
@@ -18834,7 +18833,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="733" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="733" spans="4:6">
       <c r="D733" t="s">
         <v>955</v>
       </c>
@@ -18845,7 +18844,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="734" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="734" spans="4:6">
       <c r="D734" t="s">
         <v>956</v>
       </c>
@@ -18856,7 +18855,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="735" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="735" spans="4:6">
       <c r="D735" t="s">
         <v>957</v>
       </c>
@@ -18867,7 +18866,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="736" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="736" spans="4:6">
       <c r="D736" t="s">
         <v>958</v>
       </c>
@@ -18878,7 +18877,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="737" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="737" spans="4:6">
       <c r="D737" t="s">
         <v>959</v>
       </c>
@@ -18889,7 +18888,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="738" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="738" spans="4:6">
       <c r="D738" t="s">
         <v>960</v>
       </c>
@@ -18900,7 +18899,7 @@
         <v>2256</v>
       </c>
     </row>
-    <row r="739" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="739" spans="4:6">
       <c r="D739" t="s">
         <v>953</v>
       </c>
@@ -18911,7 +18910,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="740" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="740" spans="4:6">
       <c r="D740" t="s">
         <v>954</v>
       </c>
@@ -18922,7 +18921,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="741" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="741" spans="4:6">
       <c r="D741" t="s">
         <v>955</v>
       </c>
@@ -18933,7 +18932,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="742" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="742" spans="4:6">
       <c r="D742" t="s">
         <v>956</v>
       </c>
@@ -18944,7 +18943,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="743" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="743" spans="4:6">
       <c r="D743" t="s">
         <v>957</v>
       </c>
@@ -18955,7 +18954,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="744" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="744" spans="4:6">
       <c r="D744" t="s">
         <v>958</v>
       </c>
@@ -18966,7 +18965,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="745" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="745" spans="4:6">
       <c r="D745" t="s">
         <v>959</v>
       </c>
@@ -18977,7 +18976,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="746" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="746" spans="4:6">
       <c r="D746" t="s">
         <v>961</v>
       </c>
@@ -18988,7 +18987,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="747" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="747" spans="4:6">
       <c r="D747" t="s">
         <v>962</v>
       </c>
@@ -18999,7 +18998,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="748" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="748" spans="4:6">
       <c r="D748" t="s">
         <v>963</v>
       </c>
@@ -19010,7 +19009,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="749" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="749" spans="4:6">
       <c r="D749" t="s">
         <v>964</v>
       </c>
@@ -19021,7 +19020,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="750" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="750" spans="4:6">
       <c r="D750" t="s">
         <v>965</v>
       </c>
@@ -19032,7 +19031,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="751" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="751" spans="4:6">
       <c r="D751" t="s">
         <v>966</v>
       </c>
@@ -19043,7 +19042,7 @@
         <v>2262</v>
       </c>
     </row>
-    <row r="752" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="752" spans="4:6">
       <c r="D752" t="s">
         <v>967</v>
       </c>
@@ -19054,7 +19053,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="753" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="753" spans="4:6">
       <c r="D753" t="s">
         <v>968</v>
       </c>
@@ -19065,7 +19064,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="754" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="754" spans="4:6">
       <c r="D754" t="s">
         <v>969</v>
       </c>
@@ -19076,7 +19075,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="755" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="755" spans="4:6">
       <c r="D755" t="s">
         <v>970</v>
       </c>
@@ -19087,7 +19086,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="756" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="756" spans="4:6">
       <c r="D756" t="s">
         <v>971</v>
       </c>
@@ -19098,7 +19097,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="757" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="757" spans="4:6">
       <c r="D757" t="s">
         <v>972</v>
       </c>
@@ -19109,7 +19108,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="758" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="758" spans="4:6">
       <c r="D758" t="s">
         <v>973</v>
       </c>
@@ -19120,7 +19119,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="759" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="759" spans="4:6">
       <c r="D759" t="s">
         <v>974</v>
       </c>
@@ -19131,7 +19130,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="760" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="760" spans="4:6">
       <c r="D760" t="s">
         <v>975</v>
       </c>
@@ -19142,7 +19141,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="761" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="761" spans="4:6">
       <c r="D761" t="s">
         <v>976</v>
       </c>
@@ -19153,7 +19152,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="762" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="762" spans="4:6">
       <c r="D762" t="s">
         <v>977</v>
       </c>
@@ -19164,7 +19163,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="763" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="763" spans="4:6">
       <c r="D763" t="s">
         <v>978</v>
       </c>
@@ -19175,7 +19174,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="764" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="764" spans="4:6">
       <c r="D764" t="s">
         <v>979</v>
       </c>
@@ -19186,7 +19185,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="765" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="765" spans="4:6">
       <c r="D765" t="s">
         <v>980</v>
       </c>
@@ -19197,7 +19196,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="766" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="766" spans="4:6">
       <c r="D766" t="s">
         <v>981</v>
       </c>
@@ -19208,7 +19207,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="767" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="767" spans="4:6">
       <c r="D767" t="s">
         <v>982</v>
       </c>
@@ -19219,7 +19218,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="768" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="768" spans="4:6">
       <c r="D768" t="s">
         <v>983</v>
       </c>
@@ -19230,7 +19229,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="769" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="769" spans="4:6">
       <c r="D769" t="s">
         <v>984</v>
       </c>
@@ -19241,7 +19240,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="770" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="770" spans="4:6">
       <c r="D770" t="s">
         <v>985</v>
       </c>
@@ -19252,7 +19251,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="771" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="771" spans="4:6">
       <c r="D771" t="s">
         <v>986</v>
       </c>
@@ -19263,7 +19262,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="772" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="772" spans="4:6">
       <c r="D772" t="s">
         <v>987</v>
       </c>
@@ -19274,7 +19273,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="773" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="773" spans="4:6">
       <c r="D773" t="s">
         <v>988</v>
       </c>
@@ -19285,7 +19284,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="774" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="774" spans="4:6">
       <c r="D774" t="s">
         <v>989</v>
       </c>
@@ -19296,7 +19295,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="775" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="775" spans="4:6">
       <c r="D775" t="s">
         <v>990</v>
       </c>
@@ -19307,7 +19306,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="776" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="776" spans="4:6">
       <c r="D776" t="s">
         <v>991</v>
       </c>
@@ -19318,7 +19317,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="777" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="777" spans="4:6">
       <c r="D777" t="s">
         <v>992</v>
       </c>
@@ -19329,7 +19328,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="778" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="778" spans="4:6">
       <c r="D778" t="s">
         <v>993</v>
       </c>
@@ -19340,7 +19339,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="779" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="779" spans="4:6">
       <c r="D779" t="s">
         <v>994</v>
       </c>
@@ -19351,7 +19350,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="780" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="780" spans="4:6">
       <c r="D780" t="s">
         <v>995</v>
       </c>
@@ -19362,7 +19361,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="781" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="781" spans="4:6">
       <c r="D781" t="s">
         <v>996</v>
       </c>
@@ -19373,7 +19372,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="782" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="782" spans="4:6">
       <c r="D782" t="s">
         <v>997</v>
       </c>
@@ -19384,7 +19383,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="783" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="783" spans="4:6">
       <c r="D783" t="s">
         <v>998</v>
       </c>
@@ -19395,7 +19394,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="784" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="784" spans="4:6">
       <c r="D784" t="s">
         <v>999</v>
       </c>
@@ -19406,7 +19405,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="785" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="785" spans="4:6">
       <c r="D785" t="s">
         <v>1000</v>
       </c>
@@ -19417,7 +19416,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="786" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="786" spans="4:6">
       <c r="D786" t="s">
         <v>1001</v>
       </c>
@@ -19428,7 +19427,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="787" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="787" spans="4:6">
       <c r="D787" t="s">
         <v>1002</v>
       </c>
@@ -19439,7 +19438,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="788" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="788" spans="4:6">
       <c r="D788" t="s">
         <v>1003</v>
       </c>
@@ -19450,7 +19449,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="789" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="789" spans="4:6">
       <c r="D789" t="s">
         <v>1004</v>
       </c>
@@ -19461,7 +19460,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="790" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="790" spans="4:6">
       <c r="D790" t="s">
         <v>1005</v>
       </c>
@@ -19472,7 +19471,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="791" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="791" spans="4:6">
       <c r="D791" t="s">
         <v>1006</v>
       </c>
@@ -19483,7 +19482,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="792" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="792" spans="4:6">
       <c r="D792" t="s">
         <v>1007</v>
       </c>
@@ -19494,7 +19493,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="793" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="793" spans="4:6">
       <c r="D793" t="s">
         <v>1008</v>
       </c>
@@ -19505,7 +19504,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="794" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="794" spans="4:6">
       <c r="D794" t="s">
         <v>1009</v>
       </c>
@@ -19516,7 +19515,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="795" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="795" spans="4:6">
       <c r="D795" t="s">
         <v>1010</v>
       </c>
@@ -19527,7 +19526,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="796" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="796" spans="4:6">
       <c r="D796" t="s">
         <v>1011</v>
       </c>
@@ -19538,7 +19537,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="797" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="797" spans="4:6">
       <c r="D797" t="s">
         <v>1012</v>
       </c>
@@ -19549,7 +19548,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="798" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="798" spans="4:6">
       <c r="D798" t="s">
         <v>1013</v>
       </c>
@@ -19560,7 +19559,7 @@
         <v>2309</v>
       </c>
     </row>
-    <row r="799" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="799" spans="4:6">
       <c r="D799" t="s">
         <v>1014</v>
       </c>
@@ -19571,7 +19570,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="800" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="800" spans="4:6">
       <c r="D800" t="s">
         <v>1015</v>
       </c>
@@ -19582,7 +19581,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="801" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="801" spans="4:6">
       <c r="D801" t="s">
         <v>1016</v>
       </c>
@@ -19593,7 +19592,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="802" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="802" spans="4:6">
       <c r="D802" t="s">
         <v>1017</v>
       </c>
@@ -19604,7 +19603,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="803" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="803" spans="4:6">
       <c r="D803" t="s">
         <v>1018</v>
       </c>
@@ -19615,7 +19614,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="804" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="804" spans="4:6">
       <c r="D804" t="s">
         <v>1019</v>
       </c>
@@ -19626,7 +19625,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="805" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="805" spans="4:6">
       <c r="D805" t="s">
         <v>1020</v>
       </c>
@@ -19637,7 +19636,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="806" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="806" spans="4:6">
       <c r="D806" t="s">
         <v>1021</v>
       </c>
@@ -19648,7 +19647,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="807" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="807" spans="4:6">
       <c r="D807" t="s">
         <v>1022</v>
       </c>
@@ -19659,7 +19658,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="808" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="808" spans="4:6">
       <c r="D808" t="s">
         <v>1023</v>
       </c>
@@ -19670,7 +19669,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="809" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="809" spans="4:6">
       <c r="D809" t="s">
         <v>1024</v>
       </c>
@@ -19681,7 +19680,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="810" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="810" spans="4:6">
       <c r="D810" t="s">
         <v>1025</v>
       </c>
@@ -19692,7 +19691,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="811" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="811" spans="4:6">
       <c r="D811" t="s">
         <v>1018</v>
       </c>
@@ -19703,7 +19702,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="812" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="812" spans="4:6">
       <c r="D812" t="s">
         <v>1019</v>
       </c>
@@ -19714,7 +19713,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="813" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="813" spans="4:6">
       <c r="D813" t="s">
         <v>1020</v>
       </c>
@@ -19725,7 +19724,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="814" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="814" spans="4:6">
       <c r="D814" t="s">
         <v>1021</v>
       </c>
@@ -19736,7 +19735,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="815" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="815" spans="4:6">
       <c r="D815" t="s">
         <v>1022</v>
       </c>
@@ -19747,7 +19746,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="816" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="816" spans="4:6">
       <c r="D816" t="s">
         <v>1023</v>
       </c>
@@ -19758,7 +19757,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="817" spans="4:6" x14ac:dyDescent="0.3">
+    <row r="817" spans="4:6">
       <c r="D817" t="s">
         <v>1024</v>
       </c>
